--- a/bug-reports.xlsx
+++ b/bug-reports.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Reports" sheetId="1" r:id="Reb5a6ae7a9bf4709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баг-репорты" sheetId="1" r:id="Re8fa6316fbbf4ca3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -90,18 +90,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugReportsTable" displayName="BugReportsTable" ref="A4:J8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Баг-репортыTable" displayName="Баг-репортыTable" ref="A4:M8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Severity"/>
-    <x:tableColumn id="3" name="Status"/>
-    <x:tableColumn id="4" name="Title"/>
-    <x:tableColumn id="5" name="Summary"/>
-    <x:tableColumn id="6" name="Steps to reproduce"/>
-    <x:tableColumn id="7" name="Expected result"/>
-    <x:tableColumn id="8" name="Actual result"/>
-    <x:tableColumn id="9" name="Related test"/>
-    <x:tableColumn id="10" name="Observed"/>
+    <x:tableColumn id="3" name="Priority"/>
+    <x:tableColumn id="4" name="Статус"/>
+    <x:tableColumn id="5" name="Заголовок"/>
+    <x:tableColumn id="6" name="Окружение"/>
+    <x:tableColumn id="7" name="Предусловия"/>
+    <x:tableColumn id="8" name="Запрос / данные"/>
+    <x:tableColumn id="9" name="Шаги воспроизведения"/>
+    <x:tableColumn id="10" name="Ожидаемый результат"/>
+    <x:tableColumn id="11" name="Фактический результат"/>
+    <x:tableColumn id="12" name="Воспроизводимость / примечание"/>
+    <x:tableColumn id="13" name="Связанный тест"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -303,20 +306,23 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="44" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="50" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="58" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="52" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="48" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="58" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="42" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
       <x:c r="A2" s="1" t="str">
-        <x:v>Bug Reports</x:v>
+        <x:v>Баг-репорты</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -327,167 +333,216 @@
         <x:v>Severity</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Status</x:v>
+        <x:v>Priority</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>Title</x:v>
+        <x:v>Статус</x:v>
       </x:c>
       <x:c r="E4" s="7" t="str">
-        <x:v>Summary</x:v>
+        <x:v>Заголовок</x:v>
       </x:c>
       <x:c r="F4" s="7" t="str">
-        <x:v>Steps to reproduce</x:v>
+        <x:v>Окружение</x:v>
       </x:c>
       <x:c r="G4" s="7" t="str">
-        <x:v>Expected result</x:v>
+        <x:v>Предусловия</x:v>
       </x:c>
       <x:c r="H4" s="7" t="str">
-        <x:v>Actual result</x:v>
+        <x:v>Запрос / данные</x:v>
       </x:c>
       <x:c r="I4" s="7" t="str">
-        <x:v>Related test</x:v>
+        <x:v>Шаги воспроизведения</x:v>
       </x:c>
       <x:c r="J4" s="7" t="str">
-        <x:v>Observed</x:v>
+        <x:v>Ожидаемый результат</x:v>
+      </x:c>
+      <x:c r="K4" s="7" t="str">
+        <x:v>Фактический результат</x:v>
+      </x:c>
+      <x:c r="L4" s="7" t="str">
+        <x:v>Воспроизводимость / примечание</x:v>
+      </x:c>
+      <x:c r="M4" s="7" t="str">
+        <x:v>Связанный тест</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="4" t="str">
         <x:v>RB-001</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>High</x:v>
+        <x:v>Высокая</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
-        <x:v>Open</x:v>
+        <x:v>Высокий</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>GET /booking ignores a matching checkin filter</x:v>
+        <x:v>Открыт</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>A booking with checkin 2031-07-10 is returned by an exact name search but not by checkin=2031-07-10.</x:v>
+        <x:v>GET /booking не возвращает бронь при точном фильтре checkin</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>1. Create a unique booking with checkin 2031-07-10 and checkout 2031-07-12.
-2. Confirm it by name filter.
-3. GET /booking?checkin=2031-07-10.</x:v>
+        <x:v>https://restful-booker.herokuapp.com; Postman; проверено 01.10.2026</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
-        <x:v>The response contains the created bookingid because documentation states checkin must be greater than or equal to the filter.</x:v>
+        <x:v>Создана бронь; bookingid сохранён.</x:v>
       </x:c>
       <x:c r="H5" s="4" t="str">
-        <x:v>200 OK with an empty array. Reproduced twice, including after a two-second delay.</x:v>
+        <x:v>GET /booking?checkin=2031-07-10&amp;checkout=2031-07-12</x:v>
       </x:c>
       <x:c r="I5" s="4" t="str">
+        <x:v>1. Создать уникальную бронь с checkin=2031-07-10 и checkout=2031-07-12.
+2. Убедиться, что она находится фильтром по имени.
+3. Выполнить запрос с точными датами.</x:v>
+      </x:c>
+      <x:c r="J5" s="4" t="str">
+        <x:v>200 OK; массив содержит bookingid созданной брони, поскольку документация задаёт условие «больше или равно».</x:v>
+      </x:c>
+      <x:c r="K5" s="4" t="str">
+        <x:v>HTTP 200
+[]</x:v>
+      </x:c>
+      <x:c r="L5" s="4" t="str">
+        <x:v>Воспроизводится 2 из 2, в том числе после задержки 2 секунды.</x:v>
+      </x:c>
+      <x:c r="M5" s="4" t="str">
         <x:v>LIST-03</x:v>
       </x:c>
-      <x:c r="J5" s="4" t="str">
-        <x:v>2026-10-01</x:v>
-      </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="72" customHeight="1">
       <x:c r="A6" s="8" t="str">
         <x:v>RB-002</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Средняя</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
-        <x:v>Open</x:v>
+        <x:v>Средний</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
-        <x:v>POST /booking accepts checkout earlier than checkin</x:v>
+        <x:v>Открыт</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str">
-        <x:v>The API stores a chronologically invalid stay.</x:v>
+        <x:v>POST /booking принимает дату выезда раньше даты заезда</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>1. POST a booking with checkin 2030-05-12 and checkout 2030-05-10.
-2. Inspect the response.</x:v>
+        <x:v>https://restful-booker.herokuapp.com; Postman; проверено 01.10.2026</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>A 4xx validation response; no booking is created.</x:v>
+        <x:v>Сервис доступен.</x:v>
       </x:c>
       <x:c r="H6" s="8" t="str">
-        <x:v>200 OK; booking was created with the reversed dates.</x:v>
+        <x:v>{"firstname":"QA","lastname":"Dates","totalprice":1,"depositpaid":true,"bookingdates":{"checkin":"2030-05-12","checkout":"2030-05-10"},"additionalneeds":"None"}</x:v>
       </x:c>
       <x:c r="I6" s="8" t="str">
+        <x:v>1. Отправить POST /booking с обратным порядком дат.
+2. Проверить статус и тело.</x:v>
+      </x:c>
+      <x:c r="J6" s="8" t="str">
+        <x:v>4xx; бронь не создаётся.</x:v>
+      </x:c>
+      <x:c r="K6" s="8" t="str">
+        <x:v>HTTP 200
+{"bookingid":94,"booking":{"firstname":"QA","lastname":"Dates","totalprice":1,"depositpaid":true,"bookingdates":{"checkin":"2030-05-12","checkout":"2030-05-10"},"additionalneeds":"None"}}</x:v>
+      </x:c>
+      <x:c r="L6" s="8" t="str">
+        <x:v>Воспроизводится 1 из 1. Тестовая запись удалена.</x:v>
+      </x:c>
+      <x:c r="M6" s="8" t="str">
         <x:v>CREATE-05</x:v>
       </x:c>
-      <x:c r="J6" s="8" t="str">
-        <x:v>2026-10-01</x:v>
-      </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="72" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>RB-003</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Средняя</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>Open</x:v>
+        <x:v>Средний</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>POST /booking accepts a missing documented required field</x:v>
+        <x:v>Открыт</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>The documentation marks additionalneeds as required, but the server accepts a request without it.</x:v>
+        <x:v>POST /booking принимает запрос без обязательного additionalneeds</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>1. POST a valid booking body without additionalneeds.
-2. Inspect the response.</x:v>
+        <x:v>https://restful-booker.herokuapp.com; Postman; проверено 01.10.2026</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>A 4xx validation response; no booking is created.</x:v>
+        <x:v>Сервис доступен.</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>200 OK; a booking without additionalneeds was created.</x:v>
+        <x:v>{"firstname":"QA","lastname":"Missing","totalprice":1,"depositpaid":true,"bookingdates":{"checkin":"2030-05-10","checkout":"2030-05-12"}}</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
+        <x:v>1. Отправить POST /booking без additionalneeds.
+2. Проверить статус и тело.</x:v>
+      </x:c>
+      <x:c r="J7" s="4" t="str">
+        <x:v>4xx; бронь не создаётся, поскольку поле отмечено обязательным в документации.</x:v>
+      </x:c>
+      <x:c r="K7" s="4" t="str">
+        <x:v>HTTP 200
+{"bookingid":85,"booking":{"firstname":"QA","lastname":"Missing","totalprice":1,"depositpaid":true,"bookingdates":{"checkin":"2030-05-10","checkout":"2030-05-12"}}}</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="str">
+        <x:v>Воспроизводится 1 из 1. Тестовая запись удалена.</x:v>
+      </x:c>
+      <x:c r="M7" s="4" t="str">
         <x:v>CREATE-04</x:v>
       </x:c>
-      <x:c r="J7" s="4" t="str">
-        <x:v>2026-10-01</x:v>
-      </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="8" t="str">
         <x:v>RB-004</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>High</x:v>
+        <x:v>Высокая</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>Open</x:v>
+        <x:v>Высокий</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>POST /booking returns 500 for invalid field types</x:v>
+        <x:v>Открыт</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
-        <x:v>Client input errors are handled as an internal server error.</x:v>
+        <x:v>POST /booking возвращает 500 при неверных типах полей</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>1. POST firstname as number, lastname as boolean, totalprice as string, depositpaid as string, and invalid date strings.
-2. Inspect status and body.</x:v>
+        <x:v>https://restful-booker.herokuapp.com; Postman; проверено 01.10.2026</x:v>
       </x:c>
       <x:c r="G8" s="8" t="str">
-        <x:v>A 4xx validation response describing invalid fields; service stays healthy.</x:v>
+        <x:v>Сервис доступен.</x:v>
       </x:c>
       <x:c r="H8" s="8" t="str">
-        <x:v>500 Internal Server Error with plain-text body Internal Server Error.</x:v>
+        <x:v>{"firstname":123,"lastname":false,"totalprice":"free","depositpaid":"yes","bookingdates":{"checkin":"not-a-date","checkout":"also-bad"},"additionalneeds":42}</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
+        <x:v>1. Отправить POST /booking с указанным телом.
+2. Проверить статус и тело ответа.</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="str">
+        <x:v>4xx с описанием ошибок валидации; сервис остаётся работоспособным.</x:v>
+      </x:c>
+      <x:c r="K8" s="8" t="str">
+        <x:v>HTTP 500 Internal Server Error
+Internal Server Error</x:v>
+      </x:c>
+      <x:c r="L8" s="8" t="str">
+        <x:v>Воспроизводится 1 из 1. Ошибка клиента не должна приводить к 5xx.</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="str">
         <x:v>CREATE-06</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="str">
-        <x:v>2026-10-01</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1729e8427b5b490c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a1c4cced53a43d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>